--- a/stories/arbres/ATOM-SEC.MAI.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam joue dans le salon. Papa plie le linge. Adam a des voitures. Les voitures sont rouges. Adam veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Adam appelle papa. Il dit : papa, la lumière. Papa vient. Papa allume. La pièce est claire. Maman entre. Maman dit : on appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Adam reprend une voiture. Il fait une route. Papa dit : les prises sont pour les adultes. Adam tient les jouets.</t>
+          <t>Adam joue dans le salon. Papa plie le linge. Adam a des voitures. Les voitures sont rouges. Adam veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Adam appelle papa. Papa, la lumière. Papa vient. Papa allume. La pièce est claire. Maman entre. On appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Adam reprend une voiture. Il fait une route. Les prises sont pour les adultes. Adam tient les jouets.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Adam joue dans le salon. Papa plie le linge. Adam a des voitures. Les voitures sont rouges. Adam veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Adam appelle papa.
+narrateur|Papa, la lumière. Papa vient. Papa allume.
+narrateur|La pièce est claire. Maman entre.
+maman|On appelle un adulte. On appelle papa ou maman.
+narrateur|Les mains restent avec les jouets. Adam reprend une voiture. Il fait une route.
+papa|Les prises sont pour les adultes.
+narrateur|Adam tient les jouets.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Adam veut la lumière. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1673,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1840,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pousse une voiture. La lumière reste allumée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2007,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Adam tient les jouets.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1513,7 @@
           <t>narrateur|Adam veut la lumière. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1678,6 +1689,7 @@
           <t>narrateur|Adam a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1857,11 @@
           <t>narrateur|Adam pousse une voiture. La lumière reste allumée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2072,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2287,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adam appelle pour la lumière</t>
+          <t>La petite voiture sous le rideau</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le rideau bouge. Une voiture rouge attend. Amir veut la lumière. Il va appeler un adulte. Les mains avec les jouets.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam joue dans le salon. Papa plie le linge. Adam a des voitures. Les voitures sont rouges. Adam veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Adam appelle papa. Papa, la lumière. Papa vient. Papa allume. La pièce est claire. Maman entre. On appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Adam reprend une voiture. Il fait une route. Les prises sont pour les adultes. Adam tient les jouets.</t>
+          <t>Le rideau bouge, tout doux. Un peu de vent. Le salon sent le linge. Papa plie une serviette. Elle est encore un peu chaude. Une voiture rouge attend. Elle est sous la table. Le tapis est doux, un peu épais. Un rayon glisse sur le bois. Il est long, tout pâle. Amir vit ici. Avec papa et maman. Une autre voiture attend. Elle est bleue, près du canapé. Papa, le rideau bouge ! Oui. C'est le vent. Tu vois ta voiture ? Oui. Elle est rouge. En ce moment, Amir joue. Il tient la voiture. Il la pose sur le tapis. La pièce est un peu sombre. Le rayon pâle ne suffit plus. Papa, la lumière. Amir regarde ses mains. Les mains avec les jouets. Amir appelle papa. On va appeler un adulte. J'arrive, Amir. Papa vient. Papa allume. La pièce est claire. Tu as appelé un adulte ? Oui, maman. Bravo, Amir. On appelle papa ou maman. Les prises sont pour les adultes. Les mains avec les jouets. Amir reprend la voiture. Il fait une petite route. La voiture roule tout doux. Vroum. Bien roulé. Tu as fait du bon travail. Maman entre. Elle pose une serviette. Tes mains sont avec les jouets ? Oui. Bravo. Amir pousse la voiture rouge. Puis la bleue. Le tapis fait un bruit doux. Tu joues encore ? Oui, papa. Ils font un garage avec un livre. Le livre est épais. Tu ranges une voiture ? Dans le garage. Bravo. La lumière reste allumée. Le rideau ne bouge plus. La voiture rouge brille. J'ai appelé un adulte. Oui. C'est bien. Amir est calme. Les mains tiennent les jouets. La serviette sent encore le chaud. Le canapé est tout calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,82 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Adam joue dans le salon. Papa plie le linge. Adam a des voitures. Les voitures sont rouges. Adam veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Adam appelle papa.
-narrateur|Papa, la lumière. Papa vient. Papa allume.
-narrateur|La pièce est claire. Maman entre.
-maman|On appelle un adulte. On appelle papa ou maman.
-narrateur|Les mains restent avec les jouets. Adam reprend une voiture. Il fait une route.
+          <t>narrateur|Le rideau bouge, tout doux.
+narrateur|Un peu de vent.
+narrateur|Le salon sent le linge.
+narrateur|Papa plie une serviette.
+narrateur|Elle est encore un peu chaude.
+narrateur|Une voiture rouge attend.
+narrateur|Elle est sous la table.
+narrateur|Le tapis est doux, un peu épais.
+narrateur|Un rayon glisse sur le bois.
+narrateur|Il est long, tout pâle.
+narrateur|Amir vit ici.
+narrateur|Avec papa et maman.
+narrateur|Une autre voiture attend.
+narrateur|Elle est bleue, près du canapé.
+enfant-m|Papa, le rideau bouge !
+papa|Oui.
+papa|C'est le vent.
+papa|Tu vois ta voiture ?
+enfant-m|Oui.
+enfant-m|Elle est rouge.
+narrateur|En ce moment, Amir joue.
+narrateur|Il tient la voiture.
+narrateur|Il la pose sur le tapis.
+narrateur|La pièce est un peu sombre.
+narrateur|Le rayon pâle ne suffit plus.
+enfant-m|Papa, la lumière.
+narrateur|Amir regarde ses mains.
+narrateur|Les mains avec les jouets.
+narrateur|Amir appelle papa.
+narrateur|On va appeler un adulte.
+papa|J'arrive, Amir.
+narrateur|Papa vient.
+narrateur|Papa allume.
+narrateur|La pièce est claire.
+maman|Tu as appelé un adulte ?
+enfant-m|Oui, maman.
+maman|Bravo, Amir.
+maman|On appelle papa ou maman.
 papa|Les prises sont pour les adultes.
-narrateur|Adam tient les jouets.</t>
+papa|Les mains avec les jouets.
+narrateur|Amir reprend la voiture.
+narrateur|Il fait une petite route.
+narrateur|La voiture roule tout doux.
+enfant-m|Vroum.
+papa|Bien roulé.
+papa|Tu as fait du bon travail.
+narrateur|Maman entre.
+narrateur|Elle pose une serviette.
+maman|Tes mains sont avec les jouets ?
+enfant-m|Oui.
+maman|Bravo.
+narrateur|Amir pousse la voiture rouge.
+narrateur|Puis la bleue.
+narrateur|Le tapis fait un bruit doux.
+papa|Tu joues encore ?
+enfant-m|Oui, papa.
+narrateur|Ils font un garage avec un livre.
+narrateur|Le livre est épais.
+papa|Tu ranges une voiture ?
+enfant-m|Dans le garage.
+papa|Bravo.
+narrateur|La lumière reste allumée.
+narrateur|Le rideau ne bouge plus.
+narrateur|La voiture rouge brille.
+enfant-m|J'ai appelé un adulte.
+papa|Oui.
+papa|C'est bien.
+narrateur|Amir est calme.
+narrateur|Les mains tiennent les jouets.
+narrateur|La serviette sent encore le chaud.
+narrateur|Le canapé est tout calme.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>voiture_passe</t>
+          <t>voitures</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1426,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Adam veut la lumière. Que fait-il ?</t>
+          <t>Amir veut la lumière. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1510,7 +1586,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Adam veut la lumière. Que fait-il ?</t>
+          <t>narrateur|Amir veut la lumière.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1538,7 +1615,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+          <t>Amir a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Papa. Bravo, Amir. Tu as fait du bon travail. Les prises sont pour les adultes. La voiture rouge reste dans la main.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,7 +1763,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Adam a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+          <t>narrateur|Amir a appelé un adulte.
+narrateur|Les mains avec les jouets.
+papa|Tu as appelé un adulte ?
+enfant-m|Oui.
+enfant-m|Papa.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+papa|Les prises sont pour les adultes.
+narrateur|La voiture rouge reste dans la main.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1714,7 +1799,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Adam pousse une voiture. La lumière reste allumée.</t>
+          <t>Amir pousse la voiture. La lumière reste allumée. Tu ranges la voiture ? Un peu. Il pose la voiture près du tapis. La bleue aussi. Tu as fini ? Oui. Bravo. La pièce est claire. Tu as appelé papa ? Oui, maman. Le rideau est calme. Le linge est plié. Le livre du garage reste ouvert.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1854,12 +1939,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Adam pousse une voiture. La lumière reste allumée.</t>
+          <t>narrateur|Amir pousse la voiture.
+narrateur|La lumière reste allumée.
+papa|Tu ranges la voiture ?
+enfant-m|Un peu.
+narrateur|Il pose la voiture près du tapis.
+narrateur|La bleue aussi.
+papa|Tu as fini ?
+enfant-m|Oui.
+papa|Bravo.
+maman|La pièce est claire.
+maman|Tu as appelé papa ?
+enfant-m|Oui, maman.
+narrateur|Le rideau est calme.
+narrateur|Le linge est plié.
+narrateur|Le livre du garage reste ouvert.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>voiture_passe</t>
+          <t>voitures</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1985,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. C'est du bon travail. La petite voiture se repose. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2026,7 +2125,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai appelé un adulte.
+enfant-m|Les mains avec les jouets.
+papa|Bravo.
+maman|C'est du bon travail.
+narrateur|La petite voiture se repose.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2048,7 +2152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2086,6 +2190,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le rideau bouge, tout doux. Un peu de vent. Le salon sent le linge. Papa plie une serviette. Elle est encore un peu chaude. Une voiture rouge attend. Elle est sous la table. Le tapis est doux, un peu épais. Un rayon glisse sur le bois. Il est long, tout pâle. Amir vit ici. Avec papa et maman. Une autre voiture attend. Elle est bleue, près du canapé. Papa, le rideau bouge ! Oui. C'est le vent. Tu vois ta voiture ? Oui. Elle est rouge. En ce moment, Amir joue. Il tient la voiture. Il la pose sur le tapis. La pièce est un peu sombre. Le rayon pâle ne suffit plus. Papa, la lumière. Amir regarde ses mains. Les mains avec les jouets. Amir appelle papa. On va appeler un adulte. J'arrive, Amir. Papa vient. Papa allume. La pièce est claire. Tu as appelé un adulte ? Oui, maman. Bravo, Amir. On appelle papa ou maman. Les prises sont pour les adultes. Les mains avec les jouets. Amir reprend la voiture. Il fait une petite route. La voiture roule tout doux. Vroum. Bien roulé. Tu as fait du bon travail. Maman entre. Elle pose une serviette. Tes mains sont avec les jouets ? Oui. Bravo. Amir pousse la voiture rouge. Puis la bleue. Le tapis fait un bruit doux. Tu joues encore ? Oui, papa. Ils font un garage avec un livre. Le livre est épais. Tu ranges une voiture ? Dans le garage. Bravo. La lumière reste allumée. Le rideau ne bouge plus. La voiture rouge brille. J'ai appelé un adulte. Oui. C'est bien. Amir est calme. Les mains tiennent les jouets. La serviette sent encore le chaud. Le canapé est tout calme.</t>
+          <t>Le rideau bouge, tout doux. Un peu de vent. Le salon sent le linge. Papa plie une serviette. Elle est encore un peu chaude. Une voiture rouge attend. Elle est sous la table. Le tapis est doux, un peu épais. Un rayon glisse sur le bois. Il est long, tout pâle. Amir vit ici. Avec papa et maman. Une autre voiture attend. Elle est bleue, près du canapé. Papa, le rideau bouge ! Oui. C'est le vent. Tu vois ta voiture ? Oui. Elle est rouge. En ce moment, Amir joue. Il tient la voiture. Il la pose sur le tapis. La pièce est un peu sombre. Le rayon pâle ne suffit plus. Papa, la lumière. Amir regarde ses mains. Les mains avec les jouets. Amir appelle papa. On va appeler un adulte. J'arrive, Amir. Papa vient. Papa allume. La pièce est claire. Tu as appelé un adulte ? Oui, maman. Bravo, Amir. On appelle papa ou maman. Les prises sont pour les adultes. Les mains avec les jouets. Amir reprend la voiture. Il fait une petite route. La voiture roule tout doux. Vroum. Bien roulé. Maman entre. Elle pose une serviette. Tes mains sont avec les jouets ? Oui. Bravo. Amir pousse la voiture rouge. Puis la bleue. Le tapis fait un bruit doux. Tu joues encore ? Oui, papa. Ils font un garage avec un livre. Le livre est épais. Tu ranges une voiture ? Dans le garage. Bravo. La lumière reste allumée. Le rideau ne bouge plus. La voiture rouge brille. J'ai appelé un adulte. Oui. C'est bien. Amir est calme. Les mains tiennent les jouets. La serviette sent encore le chaud. Le canapé est tout calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Adam joue dans le salon. Papa plie le linge. Adam a des voitures. Les voitures sont rouges. Adam veut plus de lumière. Il regarde ses &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt;. Les mains restent avec les jouets. Adam appelle papa. Il dit : papa, la lumière. Papa vient. Papa allume. La pièce est claire. Maman entre. Maman dit : on appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Adam reprend une voiture. Il fait une route. Papa dit : les prises sont pour les adultes. Adam tient les jouets.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rideau bouge, tout doux. Un peu de vent. Le salon sent le linge. Papa plie une serviette. Elle est encore un peu chaude. Une voiture rouge attend. Elle est sous la table. Le tapis est doux, un peu épais. Un rayon glisse sur le bois. Il est long, tout pâle. Amir vit ici. Avec papa et maman. Une autre voiture attend. Elle est bleue, près du canapé. Papa, le rideau bouge ! Oui. C'est le vent. Tu vois ta voiture ? Oui. Elle est rouge. En ce moment, Amir joue. Il tient la voiture. Il la pose sur le tapis. La pièce est un peu sombre. Le rayon pâle ne suffit plus. Papa, la lumière. Amir regarde ses mains. Les mains avec les jouets. Amir appelle papa. On va appeler un adulte. J'arrive, Amir. Papa vient. Papa allume. La pièce est claire. Tu as appelé un adulte ? Oui, maman. Bravo, Amir. On appelle papa ou maman. Les prises sont pour les adultes. Les mains avec les jouets. Amir reprend la voiture. Il fait une petite route. La voiture roule tout doux. Vroum. Bien roulé. Maman entre. Elle pose une serviette. Tes mains sont avec les jouets ? Oui. Bravo. Amir pousse la voiture rouge. Puis la bleue. Le tapis fait un bruit doux. Tu joues encore ? Oui, papa. Ils font un garage avec un livre. Le livre est épais. Tu ranges une voiture ? Dans le garage. Bravo. La lumière reste allumée. Le rideau ne bouge plus. La voiture rouge brille. J'ai appelé un adulte. Oui. C'est bien. Amir est calme. Les mains tiennent les jouets. La serviette sent encore le chaud. Le canapé est tout calme.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1369,7 +1369,6 @@
 narrateur|La voiture roule tout doux.
 enfant-m|Vroum.
 papa|Bien roulé.
-papa|Tu as fait du bon travail.
 narrateur|Maman entre.
 narrateur|Elle pose une serviette.
 maman|Tes mains sont avec les jouets ?
@@ -1431,7 +1430,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Adam veut la lumière. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir veut la lumière. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1590,7 +1589,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1615,12 +1613,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Papa. Bravo, Amir. Tu as fait du bon travail. Les prises sont pour les adultes. La voiture rouge reste dans la main.</t>
+          <t>Amir a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Papa. Bravo, Amir. Les prises sont pour les adultes. La voiture rouge reste dans la main.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Adam a appelé un adulte. Les &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt; étaient avec les jouets. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Papa. Bravo, Amir. Les prises sont pour les adultes. La voiture rouge reste dans la main.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1769,12 +1767,10 @@
 enfant-m|Oui.
 enfant-m|Papa.
 maman|Bravo, Amir.
-maman|Tu as fait du bon travail.
 papa|Les prises sont pour les adultes.
 narrateur|La voiture rouge reste dans la main.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1804,7 +1800,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Adam pousse une voiture. La lumière reste allumée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir pousse la voiture. La lumière reste allumée. Tu ranges la voiture ? Un peu. Il pose la voiture près du tapis. La bleue aussi. Tu as fini ? Oui. Bravo. La pièce est claire. Tu as appelé papa ? Oui, maman. Le rideau est calme. Le linge est plié. Le livre du garage reste ouvert.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1985,12 +1981,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. C'est du bon travail. La petite voiture se repose. L'histoire est finie.</t>
+          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. La petite voiture se repose.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. La petite voiture se repose.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2128,12 +2124,9 @@
           <t>enfant-m|J'ai appelé un adulte.
 enfant-m|Les mains avec les jouets.
 papa|Bravo.
-maman|C'est du bon travail.
-narrateur|La petite voiture se repose.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La petite voiture se repose.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2152,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2197,6 +2190,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, rideau, voitures rouges, linge</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adam, papa, maman</t>
+          <t>Amir, papa, maman</t>
         </is>
       </c>
     </row>
